--- a/sample/CORE_CONFIG_PROP.xlsx
+++ b/sample/CORE_CONFIG_PROP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cptkang/AIOps/collectorinfra/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BC965C-F924-D945-B6C7-017C1261632D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35A1BCA-021D-4548-807D-928C319D1679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36620" yWindow="-4460" windowWidth="34620" windowHeight="18020" xr2:uid="{BDB4665D-1951-4DCC-AD31-7E45A8987E10}"/>
+    <workbookView xWindow="1720" yWindow="660" windowWidth="30200" windowHeight="20260" xr2:uid="{BDB4665D-1951-4DCC-AD31-7E45A8987E10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -169,6 +169,691 @@
   </si>
   <si>
     <t>1703046687040</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>92590669</t>
+  </si>
+  <si>
+    <t>OSType</t>
+  </si>
+  <si>
+    <t>LINUX</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>92590674</t>
+  </si>
+  <si>
+    <t>OSVerson</t>
+  </si>
+  <si>
+    <t>Red Hat Enterprise Linux Server release 7.3 (Maipo)</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>92590692</t>
+  </si>
+  <si>
+    <t>PatchLevel</t>
+  </si>
+  <si>
+    <t>3.10.0-514.el7.x86_64</t>
+  </si>
+  <si>
+    <t>2332</t>
+  </si>
+  <si>
+    <t>92590679</t>
+  </si>
+  <si>
+    <t>SerialNumber</t>
+  </si>
+  <si>
+    <t>DFZLCM2</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>92590661</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Dell Inc.</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>92597452</t>
+  </si>
+  <si>
+    <t>1703046804811</t>
+  </si>
+  <si>
+    <t>2594314</t>
+  </si>
+  <si>
+    <t>92597444</t>
+  </si>
+  <si>
+    <t>92597421</t>
+  </si>
+  <si>
+    <t>92597431</t>
+  </si>
+  <si>
+    <t>92597437</t>
+  </si>
+  <si>
+    <t>1703046806776</t>
+  </si>
+  <si>
+    <t>92597448</t>
+  </si>
+  <si>
+    <t>92597409</t>
+  </si>
+  <si>
+    <t>92597455</t>
+  </si>
+  <si>
+    <t>1703046806555</t>
+  </si>
+  <si>
+    <t>fs.file-max = 6445470
+kernel.auto_msgmni = 1
+kernel.msgmnb = 16384
+kernel.msgmni = 32768
+kernel.sem = 250	32000	32	128
+kernel.sem_next_id = -1
+kernel.shmall = 18446744073692774399
+kernel.shmmax = 18446744073692774399
+kernel.shmmni = 4096
+net.core.rmem_default = 212992
+net.core.rmem_max = 212992
+net.core.wmem_default = 212992
+net.core.wmem_max = 212992
+net.ipv4.conf.all.arp_filter = 0
+net.ipv4.conf.all.rp_filter = 1
+net.ipv4.conf.bond0.arp_filter = 0
+net.ipv4.conf.bond0.rp_filter = 1
+net.ipv4.conf.bond1.arp_filter = 0
+net.ipv4.conf.bond1.rp_filter = 1
+net.ipv4.conf.default.arp_filter = 0
+net.ipv4.conf.default.rp_filter = 1
+net.ipv4.conf.em1.arp_filter = 0
+net.ipv4.conf.em1.rp_filter = 1
+net.ipv4.conf.em2.arp_filter = 0
+net.ipv4.conf.em2.rp_filter = 1
+net.ipv4.conf.em3.arp_filter = 0
+net.ipv4.conf.em3.rp_filter = 1
+net.ipv4.conf.em4.arp_filter = 0
+net.ipv4.conf.em4.rp_filter = 1
+net.ipv4.conf.lo.arp_filter = 0
+net.ipv4.conf.lo.rp_filter = 0
+net.ipv4.conf.p5p1.arp_filter = 0
+net.ipv4.conf.p5p1.rp_filter = 1
+net.ipv4.conf.p5p2.arp_filter = 0
+net.ipv4.conf.p5p2.rp_filter = 1
+net.ipv4.conf.p7p1.arp_filter = 0
+net.ipv4.conf.p7p1.rp_filter = 1
+net.ipv4.conf.p7p2.arp_filter = 0
+net.ipv4.conf.p7p2.rp_filter = 1
+net.ipv4.ip_local_port_range = 32768	60999
+net.ipv4.tcp_fin_timeout = 60
+net.ipv4.tcp_keepalive_time = 7200
+net.ipv4.tcp_mem = 1522701	2030270	3045402
+net.ipv4.tcp_rfc1337 = 0
+net.ipv4.tcp_rmem = 4096	87380	6291456
+net.ipv4.tcp_syncookies = 1
+net.ipv4.tcp_timestamps = 1
+net.ipv4.tcp_wmem = 4096	16384	4194304
+sunrpc.tcp_fin_timeout = 15</t>
+  </si>
+  <si>
+    <t>92597412</t>
+  </si>
+  <si>
+    <t>92597417</t>
+  </si>
+  <si>
+    <t>92597458</t>
+  </si>
+  <si>
+    <t>92597427</t>
+  </si>
+  <si>
+    <t>DFZGCM2</t>
+  </si>
+  <si>
+    <t>92597406</t>
+  </si>
+  <si>
+    <t>14346</t>
+  </si>
+  <si>
+    <t>FPU</t>
+  </si>
+  <si>
+    <t>1574822265858</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>14345</t>
+  </si>
+  <si>
+    <t>HYPERTHREADING</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>14343</t>
+  </si>
+  <si>
+    <t>LOGICALCORE</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>14336</t>
+  </si>
+  <si>
+    <t>MODEL</t>
+  </si>
+  <si>
+    <t>Intel(R) Xeon(R) CPU E5-2620 v4 @ 2.10GHz</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>14341</t>
+  </si>
+  <si>
+    <t>PHYSICALCORE</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>14339</t>
+  </si>
+  <si>
+    <t>PHYSICALCPU</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>14338</t>
+  </si>
+  <si>
+    <t>SPEED</t>
+  </si>
+  <si>
+    <t>2100.0</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>14337</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>14335</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>GenuineIntel</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>14362</t>
+  </si>
+  <si>
+    <t>TotalSize</t>
+  </si>
+  <si>
+    <t>1574822265899</t>
+  </si>
+  <si>
+    <t>62.1 GB</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>LIST</t>
+  </si>
+  <si>
+    <t>99459368</t>
+  </si>
+  <si>
+    <t>DiskColumns</t>
+  </si>
+  <si>
+    <t>1716354414043</t>
+  </si>
+  <si>
+    <t>2871542</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>99459366</t>
+  </si>
+  <si>
+    <t>DiskCount</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>99459367</t>
+  </si>
+  <si>
+    <t>1716354413992</t>
+  </si>
+  <si>
+    <t>977.3 GB</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>97983411</t>
+  </si>
+  <si>
+    <t>1713614818797</t>
+  </si>
+  <si>
+    <t>2814862</t>
+  </si>
+  <si>
+    <t>97983409</t>
+  </si>
+  <si>
+    <t>97983410</t>
+  </si>
+  <si>
+    <t>1713614818353</t>
+  </si>
+  <si>
+    <t>14472</t>
+  </si>
+  <si>
+    <t>1574822267712</t>
+  </si>
+  <si>
+    <t>1139</t>
+  </si>
+  <si>
+    <t>14437</t>
+  </si>
+  <si>
+    <t>1574822267409</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>14436</t>
+  </si>
+  <si>
+    <t>14434</t>
+  </si>
+  <si>
+    <t>14426</t>
+  </si>
+  <si>
+    <t>14431</t>
+  </si>
+  <si>
+    <t>14429</t>
+  </si>
+  <si>
+    <t>14428</t>
+  </si>
+  <si>
+    <t>14427</t>
+  </si>
+  <si>
+    <t>14425</t>
+  </si>
+  <si>
+    <t>14550</t>
+  </si>
+  <si>
+    <t>SwapTotalSize</t>
+  </si>
+  <si>
+    <t>1574822269119</t>
+  </si>
+  <si>
+    <t>3.9 GB</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>14551</t>
+  </si>
+  <si>
+    <t>TotalPageFileSize</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>21814451</t>
+  </si>
+  <si>
+    <t>BANDW</t>
+  </si>
+  <si>
+    <t>1599534984457</t>
+  </si>
+  <si>
+    <t>10 Gb</t>
+  </si>
+  <si>
+    <t>435325</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>21814453</t>
+  </si>
+  <si>
+    <t>DESC</t>
+  </si>
+  <si>
+    <t>N/S</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>21814454</t>
+  </si>
+  <si>
+    <t>DUPLEX</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>3813</t>
+  </si>
+  <si>
+    <t>21814448</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>21814447</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>b4:96:91:0e:bd:a6</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>21814452</t>
+  </si>
+  <si>
+    <t>MTU</t>
+  </si>
+  <si>
+    <t>1500.0</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>21814449</t>
+  </si>
+  <si>
+    <t>NETMASK</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>21814446</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>1599534984456</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>21814450</t>
+  </si>
+  <si>
+    <t>Ethernet</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>21814460</t>
+  </si>
+  <si>
+    <t>1599534984476</t>
+  </si>
+  <si>
+    <t>435326</t>
+  </si>
+  <si>
+    <t>21814462</t>
+  </si>
+  <si>
+    <t>21814463</t>
+  </si>
+  <si>
+    <t>21814457</t>
+  </si>
+  <si>
+    <t>200.200.220.65</t>
+  </si>
+  <si>
+    <t>21814456</t>
+  </si>
+  <si>
+    <t>b4:96:91:0e:bd:a4</t>
+  </si>
+  <si>
+    <t>21814461</t>
+  </si>
+  <si>
+    <t>21814458</t>
+  </si>
+  <si>
+    <t>21814455</t>
+  </si>
+  <si>
+    <t>21814459</t>
+  </si>
+  <si>
+    <t>15169</t>
+  </si>
+  <si>
+    <t>1574822271228</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>15170</t>
+  </si>
+  <si>
+    <t>21812553</t>
+  </si>
+  <si>
+    <t>1599534542000</t>
+  </si>
+  <si>
+    <t>435156</t>
+  </si>
+  <si>
+    <t>21812555</t>
+  </si>
+  <si>
+    <t>21812556</t>
+  </si>
+  <si>
+    <t>21812550</t>
+  </si>
+  <si>
+    <t>21812549</t>
+  </si>
+  <si>
+    <t>b4:96:91:0e:bd:6e</t>
+  </si>
+  <si>
+    <t>21812554</t>
+  </si>
+  <si>
+    <t>21812551</t>
+  </si>
+  <si>
+    <t>21812548</t>
+  </si>
+  <si>
+    <t>21812552</t>
+  </si>
+  <si>
+    <t>21812562</t>
+  </si>
+  <si>
+    <t>1599534542012</t>
+  </si>
+  <si>
+    <t>435157</t>
+  </si>
+  <si>
+    <t>21812564</t>
+  </si>
+  <si>
+    <t>21812565</t>
+  </si>
+  <si>
+    <t>21812559</t>
+  </si>
+  <si>
+    <t>200.200.220.66</t>
+  </si>
+  <si>
+    <t>21812558</t>
+  </si>
+  <si>
+    <t>b4:96:91:0e:bd:6c</t>
+  </si>
+  <si>
+    <t>21812563</t>
+  </si>
+  <si>
+    <t>21812560</t>
+  </si>
+  <si>
+    <t>21812557</t>
+  </si>
+  <si>
+    <t>21812561</t>
+  </si>
+  <si>
+    <t>MA_hostapo01_20191002170929</t>
+  </si>
+  <si>
+    <t>hostapo01</t>
+  </si>
+  <si>
+    <t>MA_hostapo02_20191002170929</t>
+  </si>
+  <si>
+    <t>hostapo02</t>
+  </si>
+  <si>
+    <t>10.2.3.1</t>
+  </si>
+  <si>
+    <t>10.2.3.2</t>
+  </si>
+  <si>
+    <t>DTYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fs.file-max = 6445469
@@ -220,693 +905,10 @@
 net.ipv4.tcp_timestamps = 1
 net.ipv4.tcp_wmem = 4096	16384	4194304
 sunrpc.tcp_fin_timeout = 15</t>
-  </si>
-  <si>
-    <t>465</t>
-  </si>
-  <si>
-    <t>92590669</t>
-  </si>
-  <si>
-    <t>OSType</t>
-  </si>
-  <si>
-    <t>LINUX</t>
-  </si>
-  <si>
-    <t>456</t>
-  </si>
-  <si>
-    <t>92590674</t>
-  </si>
-  <si>
-    <t>OSVerson</t>
-  </si>
-  <si>
-    <t>Red Hat Enterprise Linux Server release 7.3 (Maipo)</t>
-  </si>
-  <si>
-    <t>457</t>
-  </si>
-  <si>
-    <t>92590692</t>
-  </si>
-  <si>
-    <t>PatchLevel</t>
-  </si>
-  <si>
-    <t>3.10.0-514.el7.x86_64</t>
-  </si>
-  <si>
-    <t>2332</t>
-  </si>
-  <si>
-    <t>92590679</t>
-  </si>
-  <si>
-    <t>SerialNumber</t>
-  </si>
-  <si>
-    <t>DFZLCM2</t>
-  </si>
-  <si>
-    <t>459</t>
-  </si>
-  <si>
-    <t>92590661</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>Dell Inc.</t>
-  </si>
-  <si>
-    <t>454</t>
-  </si>
-  <si>
-    <t>92597452</t>
-  </si>
-  <si>
-    <t>1703046804811</t>
-  </si>
-  <si>
-    <t>2594314</t>
-  </si>
-  <si>
-    <t>92597444</t>
-  </si>
-  <si>
-    <t>92597421</t>
-  </si>
-  <si>
-    <t>92597431</t>
-  </si>
-  <si>
-    <t>92597437</t>
-  </si>
-  <si>
-    <t>1703046806776</t>
-  </si>
-  <si>
-    <t>92597448</t>
-  </si>
-  <si>
-    <t>92597409</t>
-  </si>
-  <si>
-    <t>92597455</t>
-  </si>
-  <si>
-    <t>1703046806555</t>
-  </si>
-  <si>
-    <t>fs.file-max = 6445470
-kernel.auto_msgmni = 1
-kernel.msgmnb = 16384
-kernel.msgmni = 32768
-kernel.sem = 250	32000	32	128
-kernel.sem_next_id = -1
-kernel.shmall = 18446744073692774399
-kernel.shmmax = 18446744073692774399
-kernel.shmmni = 4096
-net.core.rmem_default = 212992
-net.core.rmem_max = 212992
-net.core.wmem_default = 212992
-net.core.wmem_max = 212992
-net.ipv4.conf.all.arp_filter = 0
-net.ipv4.conf.all.rp_filter = 1
-net.ipv4.conf.bond0.arp_filter = 0
-net.ipv4.conf.bond0.rp_filter = 1
-net.ipv4.conf.bond1.arp_filter = 0
-net.ipv4.conf.bond1.rp_filter = 1
-net.ipv4.conf.default.arp_filter = 0
-net.ipv4.conf.default.rp_filter = 1
-net.ipv4.conf.em1.arp_filter = 0
-net.ipv4.conf.em1.rp_filter = 1
-net.ipv4.conf.em2.arp_filter = 0
-net.ipv4.conf.em2.rp_filter = 1
-net.ipv4.conf.em3.arp_filter = 0
-net.ipv4.conf.em3.rp_filter = 1
-net.ipv4.conf.em4.arp_filter = 0
-net.ipv4.conf.em4.rp_filter = 1
-net.ipv4.conf.lo.arp_filter = 0
-net.ipv4.conf.lo.rp_filter = 0
-net.ipv4.conf.p5p1.arp_filter = 0
-net.ipv4.conf.p5p1.rp_filter = 1
-net.ipv4.conf.p5p2.arp_filter = 0
-net.ipv4.conf.p5p2.rp_filter = 1
-net.ipv4.conf.p7p1.arp_filter = 0
-net.ipv4.conf.p7p1.rp_filter = 1
-net.ipv4.conf.p7p2.arp_filter = 0
-net.ipv4.conf.p7p2.rp_filter = 1
-net.ipv4.ip_local_port_range = 32768	60999
-net.ipv4.tcp_fin_timeout = 60
-net.ipv4.tcp_keepalive_time = 7200
-net.ipv4.tcp_mem = 1522701	2030270	3045402
-net.ipv4.tcp_rfc1337 = 0
-net.ipv4.tcp_rmem = 4096	87380	6291456
-net.ipv4.tcp_syncookies = 1
-net.ipv4.tcp_timestamps = 1
-net.ipv4.tcp_wmem = 4096	16384	4194304
-sunrpc.tcp_fin_timeout = 15</t>
-  </si>
-  <si>
-    <t>92597412</t>
-  </si>
-  <si>
-    <t>92597417</t>
-  </si>
-  <si>
-    <t>92597458</t>
-  </si>
-  <si>
-    <t>92597427</t>
-  </si>
-  <si>
-    <t>DFZGCM2</t>
-  </si>
-  <si>
-    <t>92597406</t>
-  </si>
-  <si>
-    <t>14346</t>
-  </si>
-  <si>
-    <t>FPU</t>
-  </si>
-  <si>
-    <t>1574822265858</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>14345</t>
-  </si>
-  <si>
-    <t>HYPERTHREADING</t>
-  </si>
-  <si>
-    <t>on</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>14343</t>
-  </si>
-  <si>
-    <t>LOGICALCORE</t>
-  </si>
-  <si>
-    <t>16.0</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>14336</t>
-  </si>
-  <si>
-    <t>MODEL</t>
-  </si>
-  <si>
-    <t>Intel(R) Xeon(R) CPU E5-2620 v4 @ 2.10GHz</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>14341</t>
-  </si>
-  <si>
-    <t>PHYSICALCORE</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>323</t>
-  </si>
-  <si>
-    <t>14339</t>
-  </si>
-  <si>
-    <t>PHYSICALCPU</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>14338</t>
-  </si>
-  <si>
-    <t>SPEED</t>
-  </si>
-  <si>
-    <t>2100.0</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>14337</t>
-  </si>
-  <si>
-    <t>TYPE</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>14335</t>
-  </si>
-  <si>
-    <t>VENDOR</t>
-  </si>
-  <si>
-    <t>GenuineIntel</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>14362</t>
-  </si>
-  <si>
-    <t>TotalSize</t>
-  </si>
-  <si>
-    <t>1574822265899</t>
-  </si>
-  <si>
-    <t>62.1 GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1126</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>LIST</t>
-  </si>
-  <si>
-    <t>99459368</t>
-  </si>
-  <si>
-    <t>DiskColumns</t>
-  </si>
-  <si>
-    <t>1716354414043</t>
-  </si>
-  <si>
-    <t>2871542</t>
-  </si>
-  <si>
-    <t>334</t>
-  </si>
-  <si>
-    <t>99459366</t>
-  </si>
-  <si>
-    <t>DiskCount</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>99459367</t>
-  </si>
-  <si>
-    <t>1716354413992</t>
-  </si>
-  <si>
-    <t>977.3 GB</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>97983411</t>
-  </si>
-  <si>
-    <t>1713614818797</t>
-  </si>
-  <si>
-    <t>2814862</t>
-  </si>
-  <si>
-    <t>97983409</t>
-  </si>
-  <si>
-    <t>97983410</t>
-  </si>
-  <si>
-    <t>1713614818353</t>
-  </si>
-  <si>
-    <t>14472</t>
-  </si>
-  <si>
-    <t>1574822267712</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>14437</t>
-  </si>
-  <si>
-    <t>1574822267409</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>14436</t>
-  </si>
-  <si>
-    <t>14434</t>
-  </si>
-  <si>
-    <t>14426</t>
-  </si>
-  <si>
-    <t>14431</t>
-  </si>
-  <si>
-    <t>14429</t>
-  </si>
-  <si>
-    <t>14428</t>
-  </si>
-  <si>
-    <t>14427</t>
-  </si>
-  <si>
-    <t>14425</t>
-  </si>
-  <si>
-    <t>14550</t>
-  </si>
-  <si>
-    <t>SwapTotalSize</t>
-  </si>
-  <si>
-    <t>1574822269119</t>
-  </si>
-  <si>
-    <t>3.9 GB</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>14551</t>
-  </si>
-  <si>
-    <t>TotalPageFileSize</t>
-  </si>
-  <si>
-    <t>486</t>
-  </si>
-  <si>
-    <t>21814451</t>
-  </si>
-  <si>
-    <t>BANDW</t>
-  </si>
-  <si>
-    <t>1599534984457</t>
-  </si>
-  <si>
-    <t>10 Gb</t>
-  </si>
-  <si>
-    <t>435325</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>21814453</t>
-  </si>
-  <si>
-    <t>DESC</t>
-  </si>
-  <si>
-    <t>N/S</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>21814454</t>
-  </si>
-  <si>
-    <t>DUPLEX</t>
-  </si>
-  <si>
-    <t>Full</t>
-  </si>
-  <si>
-    <t>3813</t>
-  </si>
-  <si>
-    <t>21814448</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>416</t>
-  </si>
-  <si>
-    <t>21814447</t>
-  </si>
-  <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>b4:96:91:0e:bd:a6</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>21814452</t>
-  </si>
-  <si>
-    <t>MTU</t>
-  </si>
-  <si>
-    <t>1500.0</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>21814449</t>
-  </si>
-  <si>
-    <t>NETMASK</t>
-  </si>
-  <si>
-    <t>255.255.255.0</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>21814446</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>1599534984456</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>21814450</t>
-  </si>
-  <si>
-    <t>Ethernet</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>21814460</t>
-  </si>
-  <si>
-    <t>1599534984476</t>
-  </si>
-  <si>
-    <t>435326</t>
-  </si>
-  <si>
-    <t>21814462</t>
-  </si>
-  <si>
-    <t>21814463</t>
-  </si>
-  <si>
-    <t>21814457</t>
-  </si>
-  <si>
-    <t>200.200.220.65</t>
-  </si>
-  <si>
-    <t>21814456</t>
-  </si>
-  <si>
-    <t>b4:96:91:0e:bd:a4</t>
-  </si>
-  <si>
-    <t>21814461</t>
-  </si>
-  <si>
-    <t>21814458</t>
-  </si>
-  <si>
-    <t>21814455</t>
-  </si>
-  <si>
-    <t>21814459</t>
-  </si>
-  <si>
-    <t>15169</t>
-  </si>
-  <si>
-    <t>1574822271228</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>15170</t>
-  </si>
-  <si>
-    <t>21812553</t>
-  </si>
-  <si>
-    <t>1599534542000</t>
-  </si>
-  <si>
-    <t>435156</t>
-  </si>
-  <si>
-    <t>21812555</t>
-  </si>
-  <si>
-    <t>21812556</t>
-  </si>
-  <si>
-    <t>21812550</t>
-  </si>
-  <si>
-    <t>21812549</t>
-  </si>
-  <si>
-    <t>b4:96:91:0e:bd:6e</t>
-  </si>
-  <si>
-    <t>21812554</t>
-  </si>
-  <si>
-    <t>21812551</t>
-  </si>
-  <si>
-    <t>21812548</t>
-  </si>
-  <si>
-    <t>21812552</t>
-  </si>
-  <si>
-    <t>21812562</t>
-  </si>
-  <si>
-    <t>1599534542012</t>
-  </si>
-  <si>
-    <t>435157</t>
-  </si>
-  <si>
-    <t>21812564</t>
-  </si>
-  <si>
-    <t>21812565</t>
-  </si>
-  <si>
-    <t>21812559</t>
-  </si>
-  <si>
-    <t>200.200.220.66</t>
-  </si>
-  <si>
-    <t>21812558</t>
-  </si>
-  <si>
-    <t>b4:96:91:0e:bd:6c</t>
-  </si>
-  <si>
-    <t>21812563</t>
-  </si>
-  <si>
-    <t>21812560</t>
-  </si>
-  <si>
-    <t>21812557</t>
-  </si>
-  <si>
-    <t>21812561</t>
-  </si>
-  <si>
-    <t>MA_hostapo01_20191002170929</t>
-  </si>
-  <si>
-    <t>hostapo01</t>
-  </si>
-  <si>
-    <t>MA_hostapo02_20191002170929</t>
-  </si>
-  <si>
-    <t>hostapo02</t>
-  </si>
-  <si>
-    <t>10.2.3.1</t>
-  </si>
-  <si>
-    <t>10.2.3.2</t>
-  </si>
-  <si>
-    <t>DTYPE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1297,7 +1299,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1356,7 +1358,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>17</v>
@@ -1470,7 +1472,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>17</v>
@@ -1508,7 +1510,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>17</v>
@@ -1622,7 +1624,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>45</v>
+        <v>257</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>17</v>
@@ -1634,7 +1636,7 @@
         <v>13</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1642,13 +1644,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
@@ -1660,7 +1662,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>17</v>
@@ -1672,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1680,13 +1682,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>15</v>
@@ -1698,7 +1700,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>17</v>
@@ -1710,7 +1712,7 @@
         <v>13</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1718,13 +1720,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>15</v>
@@ -1736,7 +1738,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>17</v>
@@ -1748,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1756,13 +1758,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>15</v>
@@ -1774,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>17</v>
@@ -1786,7 +1788,7 @@
         <v>13</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1794,13 +1796,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>15</v>
@@ -1812,7 +1814,7 @@
         <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>17</v>
@@ -1824,7 +1826,7 @@
         <v>13</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1908,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -1917,19 +1919,19 @@
         <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>13</v>
@@ -1946,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
@@ -1955,7 +1957,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -1967,7 +1969,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>13</v>
@@ -1984,7 +1986,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>13</v>
@@ -1993,7 +1995,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
@@ -2005,7 +2007,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>13</v>
@@ -2022,7 +2024,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>13</v>
@@ -2031,19 +2033,19 @@
         <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>13</v>
@@ -2060,7 +2062,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>13</v>
@@ -2069,7 +2071,7 @@
         <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>13</v>
@@ -2078,10 +2080,10 @@
         <v>16</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>13</v>
@@ -2098,7 +2100,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>13</v>
@@ -2107,7 +2109,7 @@
         <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>13</v>
@@ -2119,7 +2121,7 @@
         <v>36</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>13</v>
@@ -2136,7 +2138,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>13</v>
@@ -2145,7 +2147,7 @@
         <v>39</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>13</v>
@@ -2157,7 +2159,7 @@
         <v>40</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>13</v>
@@ -2174,7 +2176,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>13</v>
@@ -2183,19 +2185,19 @@
         <v>43</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="I24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>13</v>
@@ -2204,7 +2206,7 @@
         <v>13</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2212,37 +2214,37 @@
         <v>11</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="J25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2250,37 +2252,37 @@
         <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="J26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2288,37 +2290,37 @@
         <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="J27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2326,29 +2328,29 @@
         <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="J28" s="1" t="s">
         <v>13</v>
       </c>
@@ -2356,7 +2358,7 @@
         <v>13</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2364,37 +2366,37 @@
         <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="J29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2478,37 +2480,37 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2516,37 +2518,37 @@
         <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2554,37 +2556,37 @@
         <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2592,37 +2594,37 @@
         <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2630,37 +2632,37 @@
         <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2668,37 +2670,37 @@
         <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2706,37 +2708,37 @@
         <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2744,37 +2746,37 @@
         <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2782,37 +2784,37 @@
         <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2858,37 +2860,37 @@
         <v>11</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -3045,40 +3047,40 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="F47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="J47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -3086,37 +3088,37 @@
         <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="I48" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -3124,67 +3126,67 @@
         <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="I49" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="E50" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="J50" s="1" t="s">
         <v>13</v>
       </c>
@@ -3192,7 +3194,7 @@
         <v>13</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3200,37 +3202,37 @@
         <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3238,16 +3240,16 @@
         <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>13</v>
@@ -3256,10 +3258,10 @@
         <v>16</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>13</v>
@@ -3268,7 +3270,7 @@
         <v>13</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3314,37 +3316,37 @@
         <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="J54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3504,29 +3506,29 @@
         <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="J59" s="1" t="s">
         <v>13</v>
       </c>
@@ -3534,7 +3536,7 @@
         <v>13</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3542,37 +3544,37 @@
         <v>11</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H60" s="1" t="s">
+      <c r="I60" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3580,37 +3582,37 @@
         <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3618,37 +3620,37 @@
         <v>11</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3656,37 +3658,37 @@
         <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H63" s="1" t="s">
+      <c r="I63" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L63" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3694,37 +3696,37 @@
         <v>11</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H64" s="1" t="s">
+      <c r="I64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3732,37 +3734,37 @@
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L65" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3770,37 +3772,37 @@
         <v>11</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H66" s="1" t="s">
+      <c r="I66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L66" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3808,37 +3810,37 @@
         <v>11</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H67" s="1" t="s">
+      <c r="I67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -4340,37 +4342,37 @@
         <v>11</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="F81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H81" s="1" t="s">
+      <c r="J81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L81" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4378,37 +4380,37 @@
         <v>11</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L82" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4454,37 +4456,37 @@
         <v>11</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="1" t="s">
+      <c r="F84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="I84" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="1" t="s">
+      <c r="J84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4492,37 +4494,37 @@
         <v>11</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="1" t="s">
+      <c r="I85" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L85" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4530,37 +4532,37 @@
         <v>11</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="1" t="s">
+      <c r="I86" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L86" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4568,37 +4570,37 @@
         <v>11</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L87" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4606,37 +4608,37 @@
         <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="I88" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L88" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4644,37 +4646,37 @@
         <v>11</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="1" t="s">
+      <c r="I89" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4682,37 +4684,37 @@
         <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="1" t="s">
+      <c r="I90" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L90" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4720,37 +4722,37 @@
         <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="F91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="I91" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L91" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4758,37 +4760,37 @@
         <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L92" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4910,37 +4912,37 @@
         <v>11</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H96" s="1" t="s">
+      <c r="J96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L96" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4948,37 +4950,37 @@
         <v>11</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4986,37 +4988,37 @@
         <v>11</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L98" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -5024,16 +5026,16 @@
         <v>11</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>13</v>
@@ -5042,10 +5044,10 @@
         <v>16</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>13</v>
@@ -5054,7 +5056,7 @@
         <v>13</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -5062,37 +5064,37 @@
         <v>11</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -5100,37 +5102,37 @@
         <v>11</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -5138,37 +5140,37 @@
         <v>11</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L102" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -5176,28 +5178,28 @@
         <v>11</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="I103" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>13</v>
@@ -5206,7 +5208,7 @@
         <v>13</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -5214,16 +5216,16 @@
         <v>11</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>13</v>
@@ -5232,10 +5234,10 @@
         <v>16</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>13</v>
@@ -5244,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -6240,37 +6242,37 @@
         <v>11</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I131" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131" s="1" t="s">
+      <c r="J131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L131" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -6278,16 +6280,16 @@
         <v>11</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>13</v>
@@ -6299,7 +6301,7 @@
         <v>13</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J132" s="1" t="s">
         <v>13</v>
@@ -6308,7 +6310,7 @@
         <v>13</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -6468,37 +6470,37 @@
         <v>11</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I137" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H137" s="1" t="s">
+      <c r="J137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L137" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6506,37 +6508,37 @@
         <v>11</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D138" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L138" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -6544,37 +6546,37 @@
         <v>11</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -6582,16 +6584,16 @@
         <v>11</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>13</v>
@@ -6600,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>13</v>
@@ -6612,7 +6614,7 @@
         <v>13</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -6620,37 +6622,37 @@
         <v>11</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D141" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L141" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K141" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L141" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6658,37 +6660,37 @@
         <v>11</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L142" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L142" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -6696,37 +6698,37 @@
         <v>11</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L143" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J143" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L143" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6734,28 +6736,28 @@
         <v>11</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D144" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="I144" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J144" s="1" t="s">
         <v>13</v>
@@ -6764,7 +6766,7 @@
         <v>13</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6772,16 +6774,16 @@
         <v>11</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>13</v>
@@ -6790,10 +6792,10 @@
         <v>16</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>13</v>
@@ -6802,7 +6804,7 @@
         <v>13</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -7304,37 +7306,37 @@
         <v>11</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H159" s="1" t="s">
+      <c r="J159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L159" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J159" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K159" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L159" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -7342,37 +7344,37 @@
         <v>11</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D160" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L160" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J160" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K160" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -7380,37 +7382,37 @@
         <v>11</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D161" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L161" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J161" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L161" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -7418,16 +7420,16 @@
         <v>11</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>13</v>
@@ -7436,10 +7438,10 @@
         <v>16</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>13</v>
@@ -7448,7 +7450,7 @@
         <v>13</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -7456,37 +7458,37 @@
         <v>11</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L163" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I163" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -7494,37 +7496,37 @@
         <v>11</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D164" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L164" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -7532,37 +7534,37 @@
         <v>11</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D165" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L165" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L165" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -7570,28 +7572,28 @@
         <v>11</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D166" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E166" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="I166" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J166" s="1" t="s">
         <v>13</v>
@@ -7600,7 +7602,7 @@
         <v>13</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -7608,16 +7610,16 @@
         <v>11</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>13</v>
@@ -7626,10 +7628,10 @@
         <v>16</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J167" s="1" t="s">
         <v>13</v>
@@ -7638,7 +7640,7 @@
         <v>13</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="168" spans="1:12">
